--- a/exports/Estatisticas_Jogadores_FC_Andorra_Carreira.xlsx
+++ b/exports/Estatisticas_Jogadores_FC_Andorra_Carreira.xlsx
@@ -462,7 +462,7 @@
     <t>GOL</t>
   </si>
   <si>
-    <t>Goleiros</t>
+    <t>Goleiro</t>
   </si>
   <si>
     <t>07/03/2006</t>
